--- a/Pipistrelli 2023.xlsx
+++ b/Pipistrelli 2023.xlsx
@@ -573,7 +573,11 @@
           <t>Villaverla</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H3" t="n">
         <v>45.6499676</v>
       </c>
@@ -625,7 +629,11 @@
           <t>Montebello vicentino</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H4" t="n">
         <v>45.4596014</v>
       </c>
@@ -677,7 +685,11 @@
           <t>Monte di Malo</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H5" t="n">
         <v>45.6619177</v>
       </c>
@@ -785,7 +797,11 @@
           <t>Longare</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H7" t="n">
         <v>45.45985</v>
       </c>
@@ -893,7 +909,11 @@
           <t>Sandrigo</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H9" t="n">
         <v>45.661886</v>
       </c>
@@ -1001,7 +1021,11 @@
           <t>Zovencedo</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H11" t="n">
         <v>45.4300235</v>
       </c>
@@ -1221,7 +1245,11 @@
           <t>Valli del Pasubio</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H15" t="n">
         <v>45.7398938</v>
       </c>
@@ -1273,7 +1301,11 @@
           <t>Dueville</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H16" t="n">
         <v>45.6403</v>
       </c>
@@ -1325,7 +1357,11 @@
           <t>Schiavon</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H17" t="n">
         <v>45.6777651</v>
       </c>
@@ -1545,7 +1581,11 @@
           <t>Isola Vicentina</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H21" t="n">
         <v>45.6299029</v>
       </c>
@@ -1599,7 +1639,11 @@
           <t>Fara Vicentino</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H22" t="n">
         <v>45.7395927</v>
       </c>
@@ -1747,7 +1791,11 @@
           <t>Dueville</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H25" t="n">
         <v>45.6285174</v>
       </c>
@@ -1903,7 +1951,11 @@
           <t>Sarego</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H28" t="n">
         <v>45.4318813</v>
       </c>
@@ -2067,7 +2119,11 @@
           <t>Chiampo</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H31" t="n">
         <v>45.5445732</v>
       </c>
@@ -2115,7 +2171,11 @@
           <t>Valbrenta</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H32" t="n">
         <v>45.8241443</v>
       </c>
@@ -2163,7 +2223,11 @@
           <t>Longare</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H33" t="n">
         <v>45.4709699</v>
       </c>
@@ -2215,7 +2279,11 @@
           <t>Arcugnano</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H34" t="n">
         <v>45.5004723</v>
       </c>
@@ -2431,7 +2499,11 @@
           <t>Montebello Vicentino</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H38" t="n">
         <v>45.4517637</v>
       </c>
@@ -2535,7 +2607,11 @@
           <t>Grumolo delle Abbadesse</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H40" t="n">
         <v>45.5163094</v>
       </c>
@@ -2583,7 +2659,11 @@
           <t>Arcugnano</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H41" t="n">
         <v>45.48688</v>
       </c>
@@ -2635,7 +2715,11 @@
           <t>Sarego</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H42" t="n">
         <v>45.4081213</v>
       </c>
@@ -2687,7 +2771,11 @@
           <t>Monticello Conte Otto</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H43" t="n">
         <v>45.5925277</v>
       </c>
@@ -2963,7 +3051,11 @@
           <t>Zanè</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H48" t="n">
         <v>45.7201187</v>
       </c>
@@ -3017,7 +3109,11 @@
           <t>Breganze</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H49" t="n">
         <v>45.7056839</v>
       </c>
@@ -3177,7 +3273,11 @@
           <t>Sarego</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H52" t="n">
         <v>45.4081213</v>
       </c>
@@ -3285,7 +3385,11 @@
           <t>Zanè</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H54" t="n">
         <v>45.7201187</v>
       </c>
@@ -3447,7 +3551,11 @@
           <t>Camisano Vicentino</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H57" t="n">
         <v>45.5220266</v>
       </c>
@@ -3719,7 +3827,11 @@
           <t>Dueville</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H62" t="n">
         <v>45.6355174</v>
       </c>
@@ -3827,7 +3939,11 @@
           <t>Montebello Vicentino</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H64" t="n">
         <v>45.4572159</v>
       </c>
@@ -3879,7 +3995,11 @@
           <t>Campiglia dei Berici</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H65" t="n">
         <v>45.3362423</v>
       </c>
@@ -4325,7 +4445,11 @@
           <t>Breganze</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H73" t="n">
         <v>45.7034884</v>
       </c>
@@ -4377,7 +4501,11 @@
           <t>Calvene</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H74" t="n">
         <v>45.7659086</v>
       </c>
@@ -4485,7 +4613,11 @@
           <t>Montegaldella</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H76" t="n">
         <v>45.430864</v>
       </c>
@@ -4537,7 +4669,11 @@
           <t>Malo</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H77" t="n">
         <v>45.6641897</v>
       </c>
@@ -4701,7 +4837,11 @@
           <t>Malo</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H80" t="n">
         <v>45.6585696</v>
       </c>
@@ -4913,7 +5053,11 @@
           <t>Arcugnano</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H84" t="n">
         <v>45.5004723</v>
       </c>
@@ -5017,7 +5161,11 @@
           <t>Brendola</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H86" t="n">
         <v>45.4721218</v>
       </c>
@@ -5065,11 +5213,7 @@
           <t>Barbarno Mossano</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>VI</t>
-        </is>
-      </c>
+      <c r="G87" t="inlineStr"/>
       <c r="H87" t="n">
         <v>45.4083415</v>
       </c>
@@ -5121,11 +5265,7 @@
           <t>Barbarno Mossano</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>VI</t>
-        </is>
-      </c>
+      <c r="G88" t="inlineStr"/>
       <c r="H88" t="n">
         <v>45.4083415</v>
       </c>
@@ -5177,7 +5317,11 @@
           <t>Montegalda</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H89" t="n">
         <v>45.4437746</v>
       </c>
@@ -5225,7 +5369,11 @@
           <t>Cogollo del Cengio</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H90" t="n">
         <v>45.7852211</v>
       </c>
@@ -5277,11 +5425,7 @@
           <t>Barbarno Mossano</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>VI</t>
-        </is>
-      </c>
+      <c r="G91" t="inlineStr"/>
       <c r="H91" t="n">
         <v>45.4083415</v>
       </c>
@@ -5385,7 +5529,11 @@
           <t>Rosà</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H93" t="n">
         <v>45.7244163</v>
       </c>
@@ -5489,7 +5637,11 @@
           <t>Alonte</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H95" t="n">
         <v>45.3650367</v>
       </c>
@@ -5541,7 +5693,11 @@
           <t>Brendola</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H96" t="n">
         <v>45.4612318</v>
       </c>
@@ -5705,7 +5861,11 @@
           <t>Arcugnano</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H99" t="n">
         <v>45.5004723</v>
       </c>
@@ -5757,7 +5917,11 @@
           <t>Arcugnano</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr"/>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H100" t="n">
         <v>45.4930641</v>
       </c>
@@ -5865,7 +6029,11 @@
           <t>Asiago</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr"/>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H102" t="n">
         <v>45.8753771</v>
       </c>
@@ -5973,7 +6141,11 @@
           <t>Piazzola sul Brenta</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr"/>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>PD</t>
+        </is>
+      </c>
       <c r="H104" t="n">
         <v>45.5797865</v>
       </c>
@@ -6025,7 +6197,11 @@
           <t>Tezze sul Brenta</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr"/>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H105" t="n">
         <v>45.6861778</v>
       </c>
@@ -6301,7 +6477,11 @@
           <t>Arcugnano</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr"/>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H110" t="n">
         <v>45.5004723</v>
       </c>

--- a/Pipistrelli 2023.xlsx
+++ b/Pipistrelli 2023.xlsx
@@ -675,7 +675,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Monte di Malo</t>
+          <t>Monte di malo</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -729,7 +729,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Altavilla Vicentina</t>
+          <t>Altavilla vicentina</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Valli del Pasubio</t>
+          <t>Valli del pasubio</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bassano del Grappa</t>
+          <t>Bassano del grappa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bassano del Grappa</t>
+          <t>Bassano del grappa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1539,7 +1539,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Isola Vicentina</t>
+          <t>Isola vicentina</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fara Vicentino</t>
+          <t>Fara vicentino</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1645,7 +1645,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Altavilla Vicentina</t>
+          <t>Altavilla vicentina</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2312,7 +2312,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bolzano Vicentino</t>
+          <t>Bolzano vicentino</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2415,7 +2415,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Montebello Vicentino</t>
+          <t>Montebello vicentino</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Grumolo delle Abbadesse</t>
+          <t>Grumolo delle abbadesse</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2675,7 +2675,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Monticello Conte Otto</t>
+          <t>Monticello conte otto</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Montecchio Maggiore</t>
+          <t>Montecchio maggiore</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3428,7 +3428,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Camisano Vicentino</t>
+          <t>Camisano vicentino</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -3642,14 +3642,19 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Due Ville</t>
+          <t>Dueville</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>VI</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>45.8144577</v>
+        <v>45.5479</v>
       </c>
       <c r="I61" t="n">
-        <v>15.9798551</v>
+        <v>11.5446</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -3802,7 +3807,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Montebello Vicentino</t>
+          <t>Montebello vicentino</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -3856,7 +3861,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Campiglia dei Berici</t>
+          <t>Campiglia dei berici</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -3910,7 +3915,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Quinto Vicentino</t>
+          <t>Quinto vicentino</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -4723,7 +4728,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Recoaro Terme</t>
+          <t>Recoaro terme</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -4826,7 +4831,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Bassano del Grappa</t>
+          <t>Bassano del grappa</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -5174,7 +5179,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Cogollo del Cengio</t>
+          <t>Cogollo del cengio</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -5915,7 +5920,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Piazzola sul Brenta</t>
+          <t>Piazzola sul brenta</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -5969,7 +5974,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tezze sul Brenta</t>
+          <t>Tezze sul brenta</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">

--- a/Pipistrelli 2023.xlsx
+++ b/Pipistrelli 2023.xlsx
@@ -621,7 +621,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Montebello vicentino</t>
+          <t>Montebello Vicentino</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Monte di malo</t>
+          <t>Monte Di Malo</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -729,7 +729,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Altavilla vicentina</t>
+          <t>Altavilla Vicentina</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Valli del pasubio</t>
+          <t>Valli Del Pasubio</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bassano del grappa</t>
+          <t>Bassano Del Grappa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bassano del grappa</t>
+          <t>Bassano Del Grappa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1539,7 +1539,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Isola vicentina</t>
+          <t>Isola Vicentina</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fara vicentino</t>
+          <t>Fara Vicentino</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1645,7 +1645,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Altavilla vicentina</t>
+          <t>Altavilla Vicentina</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2312,7 +2312,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bolzano vicentino</t>
+          <t>Bolzano Vicentino</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2415,7 +2415,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Montebello vicentino</t>
+          <t>Montebello Vicentino</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Grumolo delle abbadesse</t>
+          <t>Grumolo Delle Abbadesse</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2675,7 +2675,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Monticello conte otto</t>
+          <t>Monticello Conte Otto</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Montecchio maggiore</t>
+          <t>Montecchio Maggiore</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3428,7 +3428,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Camisano vicentino</t>
+          <t>Camisano Vicentino</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -3807,7 +3807,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Montebello vicentino</t>
+          <t>Montebello Vicentino</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -3861,7 +3861,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Campiglia dei berici</t>
+          <t>Campiglia Dei Berici</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -3915,7 +3915,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Quinto vicentino</t>
+          <t>Quinto Vicentino</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -4728,7 +4728,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Recoaro terme</t>
+          <t>Recoaro Terme</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Bassano del grappa</t>
+          <t>Bassano Del Grappa</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -5179,7 +5179,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Cogollo del cengio</t>
+          <t>Cogollo Del Cengio</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -5920,7 +5920,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Piazzola sul brenta</t>
+          <t>Piazzola Sul Brenta</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -5974,7 +5974,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tezze sul brenta</t>
+          <t>Tezze Sul Brenta</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
